--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487073_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487073_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3557</v>
+        <v>4.0203</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1203</v>
+        <v>4.1063</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7646</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1334</v>
+        <v>4.0164</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1065</v>
+        <v>4.3955</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2399</v>
+        <v>-0.3792</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0693</v>
+        <v>5.3773</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6417</v>
+        <v>4.5227</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4277</v>
+        <v>0.8547</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9359</v>
+        <v>-1.361</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7481</v>
+        <v>-0.1272</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1878</v>
+        <v>-1.2338</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2922</v>
+        <v>-0.4822</v>
       </c>
       <c r="T2" t="n">
-        <v>1.051</v>
+        <v>-0.306</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7588</v>
+        <v>-0.1762</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3009</v>
+        <v>3.7291</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3066</v>
+        <v>5.1189</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0057</v>
+        <v>-1.3899</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0164</v>
+        <v>2.1334</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3955</v>
+        <v>-0.1065</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3792</v>
+        <v>2.2399</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3773</v>
+        <v>5.0693</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5227</v>
+        <v>0.6417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8547</v>
+        <v>4.4277</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.361</v>
+        <v>-2.9359</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1272</v>
+        <v>-0.7481</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2338</v>
+        <v>-2.1878</v>
       </c>
       <c r="P3" t="n">
-        <v>0.772</v>
+        <v>1.9301</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2016</v>
+        <v>-0.3345</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1057</v>
+        <v>0.0496</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0959</v>
+        <v>-0.3841</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5413</v>
+        <v>3.7009</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2783</v>
+        <v>2.6788</v>
       </c>
       <c r="F4" t="n">
-        <v>1.263</v>
+        <v>1.0221</v>
       </c>
       <c r="G4" t="n">
         <v>2.8545</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0853</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7588</v>
+        <v>-0.3582</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6735</v>
+        <v>0.4326</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1216</v>
+        <v>2.429</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1365</v>
+        <v>0.3367</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9852</v>
+        <v>2.0922</v>
       </c>
       <c r="G5" t="n">
         <v>3.4013</v>
@@ -844,13 +844,13 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8937</v>
+        <v>-0.5863</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5803</v>
+        <v>-0.38</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3133</v>
+        <v>-0.2062</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0636</v>
+        <v>1.9565</v>
       </c>
       <c r="E6" t="n">
         <v>0.9661999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0973</v>
+        <v>0.9902</v>
       </c>
       <c r="G6" t="n">
         <v>0.9651999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.6227</v>
       </c>
       <c r="T6" t="n">
         <v>-0.4614</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0542</v>
+        <v>-0.1613</v>
       </c>
       <c r="V6" t="n">
         <v>1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6448</v>
+        <v>1.5982</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1938</v>
+        <v>1.0937</v>
       </c>
       <c r="F7" t="n">
-        <v>0.451</v>
+        <v>0.5046</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2124</v>
@@ -1000,13 +1000,13 @@
         <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5288</v>
+        <v>-0.5754</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2247</v>
+        <v>-0.3249</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3041</v>
+        <v>-0.2505</v>
       </c>
       <c r="V7" t="n">
         <v>1.228</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1645</v>
+        <v>-1.764</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7809</v>
+        <v>-0.3803</v>
       </c>
       <c r="F8" t="n">
         <v>-1.3836</v>
@@ -1078,10 +1078,10 @@
         <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5486</v>
+        <v>-0.1481</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5949</v>
+        <v>-0.1943</v>
       </c>
       <c r="U8" t="n">
         <v>0.0462</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1493</v>
+        <v>-3.2832</v>
       </c>
       <c r="E9" t="n">
         <v>-0.959</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1903</v>
+        <v>-2.3242</v>
       </c>
       <c r="G9" t="n">
         <v>0.4688</v>
@@ -1156,13 +1156,13 @@
         <v>2.3161</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4012</v>
+        <v>0.2674</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2842</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6854</v>
+        <v>0.5516</v>
       </c>
       <c r="V9" t="n">
         <v>-3.4403</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6725</v>
+        <v>-3.7994</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4974</v>
+        <v>-4.5975</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8249</v>
+        <v>0.7981</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6201</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2637</v>
+        <v>0.1368</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0912</v>
+        <v>-0.1913</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3549</v>
+        <v>0.3282</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5971</v>
+        <v>-4.143</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.022</v>
+        <v>-1.6214</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5751</v>
+        <v>-2.5215</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0813</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7813</v>
+        <v>-0.3272</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9373</v>
+        <v>-0.5367</v>
       </c>
       <c r="U11" t="n">
-        <v>0.156</v>
+        <v>0.2095</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6996</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.444500000000002</v>
+        <v>4.444399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>6.742399999999998</v>
+        <v>6.7424</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2979</v>
+        <v>-2.298</v>
       </c>
       <c r="G12" t="n">
         <v>9.279699999999998</v>
@@ -1393,10 +1393,10 @@
         <v>-2.5978</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.9875</v>
+        <v>-2.9874</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3897</v>
+        <v>0.3897999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-6.0976</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>G. DE LA CRUZ MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7673</v>
+        <v>2.4576</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5743</v>
+        <v>3.6586</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1929</v>
+        <v>-1.201</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6791</v>
+        <v>1.5119</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.3899</v>
+        <v>-0.3053</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2892</v>
+        <v>1.8172</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5518999999999999</v>
+        <v>3.6204</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4249</v>
+        <v>1.0971</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9768</v>
+        <v>2.5233</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.231</v>
+        <v>-2.1085</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.965</v>
+        <v>-1.4023</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.266</v>
+        <v>-0.7062</v>
       </c>
       <c r="P13" t="n">
-        <v>0.772</v>
+        <v>-0.772</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6467</v>
+        <v>0.2039</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9249</v>
+        <v>0.4545</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7218</v>
+        <v>-0.2505</v>
       </c>
       <c r="V13" t="n">
-        <v>3.0277</v>
+        <v>1.5138</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0277</v>
+        <v>1.5138</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. DE LA CRUZ MARTINEZ</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7045</v>
+        <v>2.4093</v>
       </c>
       <c r="E14" t="n">
-        <v>3.959</v>
+        <v>3.5839</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2545</v>
+        <v>-1.1747</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5119</v>
+        <v>0.2008</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3053</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8172</v>
+        <v>1.1489</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6204</v>
+        <v>4.1781</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0971</v>
+        <v>1.1021</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5233</v>
+        <v>3.076</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1085</v>
+        <v>-3.9773</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4023</v>
+        <v>-2.0501</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7062</v>
+        <v>-1.9272</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>1.158</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4508</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7549</v>
+        <v>-0.155</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3041</v>
+        <v>0.9075</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5138</v>
+        <v>1.842</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5138</v>
+        <v>2.4559</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SAN JOSE GONZALEZ</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8192</v>
+        <v>1.6759</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9076</v>
+        <v>2.0722</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9115</v>
+        <v>-0.3963</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6902</v>
+        <v>-3.6791</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6624</v>
+        <v>-3.3899</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0278</v>
+        <v>-0.2892</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6564</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6157</v>
+        <v>-0.4249</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0407</v>
+        <v>0.9768</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0338</v>
+        <v>-4.231</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0466</v>
+        <v>-2.965</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0129</v>
+        <v>-1.266</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>1.129</v>
+        <v>1.5553</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2512</v>
+        <v>0.4228</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8778</v>
+        <v>1.1326</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3.0277</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.0277</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>J. SAN JOSE GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1068</v>
+        <v>1.2844</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6827</v>
+        <v>0.5071</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5759</v>
+        <v>0.7774</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2008</v>
+        <v>0.6902</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9481000000000001</v>
+        <v>0.6624</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1489</v>
+        <v>0.0278</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1781</v>
+        <v>0.6564</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1021</v>
+        <v>0.6157</v>
       </c>
       <c r="L16" t="n">
-        <v>3.076</v>
+        <v>0.0407</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.9773</v>
+        <v>0.0338</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0501</v>
+        <v>0.0466</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9272</v>
+        <v>-0.0129</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.386</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5499000000000001</v>
+        <v>0.5942</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0562</v>
+        <v>-0.1494</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5063</v>
+        <v>0.7436</v>
       </c>
       <c r="V16" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9526</v>
+        <v>-1.0656</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1985</v>
+        <v>-1.4989</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2459</v>
+        <v>0.4333</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1984</v>
@@ -1780,13 +1780,13 @@
         <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1686</v>
+        <v>0.0555</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3107</v>
+        <v>0.0103</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1421</v>
+        <v>0.0453</v>
       </c>
       <c r="V17" t="n">
         <v>0.6562</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6523</v>
+        <v>-1.5988</v>
       </c>
       <c r="E18" t="n">
         <v>-0.7271</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9252</v>
+        <v>-0.8717</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4006</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0238</v>
+        <v>0.0297</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>L. BLANCO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2126</v>
+        <v>-1.616</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1422</v>
+        <v>-1.3587</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0704</v>
+        <v>-0.2574</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0436</v>
+        <v>-0.7472</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8569</v>
+        <v>-1.0256</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1867</v>
+        <v>0.2785</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9529</v>
+        <v>0.0605</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7659</v>
+        <v>0.0362</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1871</v>
+        <v>0.0243</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9965</v>
+        <v>-0.8076</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6227</v>
+        <v>-1.0618</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3738</v>
+        <v>0.2542</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.158</v>
+        <v>-0.772</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5248</v>
+        <v>-0.0968</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7139</v>
+        <v>-0.4541</v>
       </c>
       <c r="U19" t="n">
-        <v>0.189</v>
+        <v>0.3573</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BLANCO DE LA CRUZ</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2443</v>
+        <v>-1.9657</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.559</v>
+        <v>-0.8418</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6853</v>
+        <v>-1.124</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7472</v>
+        <v>-2.0436</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0256</v>
+        <v>-0.8569</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2785</v>
+        <v>-1.1867</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0605</v>
+        <v>0.9529</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0362</v>
+        <v>0.7659</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0243</v>
+        <v>0.1871</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8076</v>
+        <v>-2.9965</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0618</v>
+        <v>-1.6227</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2542</v>
+        <v>-1.3738</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.772</v>
+        <v>-1.158</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R20" t="n">
-        <v>0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7251</v>
+        <v>-0.278</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6544</v>
+        <v>-0.4134</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0707</v>
+        <v>0.1355</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7763</v>
+        <v>-2.3162</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1715</v>
+        <v>-1.4706</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6048</v>
+        <v>-0.8457</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2121</v>
@@ -2092,13 +2092,13 @@
         <v>2.3161</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2783</v>
+        <v>0.1818</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6398</v>
+        <v>0.0612</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3615</v>
+        <v>0.1206</v>
       </c>
       <c r="V21" t="n">
         <v>0.3281</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0042</v>
+        <v>-3.0418</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0276</v>
+        <v>-1.627</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9767</v>
+        <v>-1.4148</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4017</v>
@@ -2170,13 +2170,13 @@
         <v>2.5091</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6954</v>
+        <v>0.267</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.107</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1877</v>
+        <v>0.3741</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5561</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4445</v>
+        <v>-3.7769</v>
       </c>
       <c r="E23" t="n">
         <v>2.2977</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.7425</v>
+        <v>-6.074900000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-9.2798</v>
@@ -2239,7 +2239,7 @@
         <v>-6.3302</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.8601</v>
+        <v>-3.860099999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-17.3707</v>
@@ -2248,13 +2248,13 @@
         <v>13.5105</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5978</v>
+        <v>3.265099999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3897000000000003</v>
+        <v>-0.3896</v>
       </c>
       <c r="U23" t="n">
-        <v>2.9875</v>
+        <v>3.6552</v>
       </c>
       <c r="V23" t="n">
         <v>6.0975</v>
